--- a/study_characterisrics/Additional_file_1_study_characteristics.xlsx
+++ b/study_characterisrics/Additional_file_1_study_characteristics.xlsx
@@ -51,7 +51,7 @@
     <t>Comments</t>
   </si>
   <si>
-    <t>Ceratti et al. [33]</t>
+    <t>Ceratti et al. [47]</t>
   </si>
   <si>
     <t>Belgium</t>
@@ -75,7 +75,7 @@
     <t>105,846 inpatient stays for heart failure , 127,931 for hypertension , 19,645 for pneumonia</t>
   </si>
   <si>
-    <t>Kamdje-Wabo et al. [44]</t>
+    <t>Kamdje-Wabo et al. [58]</t>
   </si>
   <si>
     <t>Germany</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">152,806 inpatient cases, 94,570 patients </t>
   </si>
   <si>
-    <t>Khoo and Hasan [48]</t>
+    <t>Khoo and Hasan [62]</t>
   </si>
   <si>
     <t>Australia</t>
@@ -138,7 +138,7 @@
     <t>Multiple condition-specific patient and procedure cohorts; no single overall study population was reported.</t>
   </si>
   <si>
-    <t>Huang et al. [49]</t>
+    <t>Huang et al. [63]</t>
   </si>
   <si>
     <t>Taiwan</t>
@@ -159,7 +159,7 @@
     <t>Approximately 23 million individuals in the complete NHIRD; a stratified sample of 3 million individuals was used for the data-quality assessment</t>
   </si>
   <si>
-    <t>Ammann et al. [39]</t>
+    <t>Ammann et al. [53]</t>
   </si>
   <si>
     <t>USA</t>
@@ -180,7 +180,7 @@
     <t>746,763 distinct health-plan members, contributing 1,116,283 eligible person-years.</t>
   </si>
   <si>
-    <t>Samples et al. [36]</t>
+    <t>Samples et al. [50]</t>
   </si>
   <si>
     <t>Observational / Retrospective</t>
@@ -216,7 +216,7 @@
     <t xml:space="preserve">3,338 patients, with 565,521 healthcare services containing diagnosis codes. </t>
   </si>
   <si>
-    <t>Miller et al. [40]</t>
+    <t>Miller et al. [54]</t>
   </si>
   <si>
     <t>Paediatric</t>
@@ -234,7 +234,7 @@
     <t xml:space="preserve">384 paediatric patients receiving 1,060 chemotherapy courses. </t>
   </si>
   <si>
-    <t>Barberio et al. [34]</t>
+    <t>Barberio et al. [48]</t>
   </si>
   <si>
     <t>Japan</t>
@@ -255,7 +255,7 @@
     <t xml:space="preserve">5,795,818 females aged 12–55 years and 717,034 infants were identified; the final linked sample contained 385,295 mother–infant pairs. </t>
   </si>
   <si>
-    <t>Gadde et al. [41]</t>
+    <t>Gadde et al. [55]</t>
   </si>
   <si>
     <t>Aggregated Medicaid-only records from a US state All-Payer Claims Database (APCD).</t>
@@ -267,7 +267,7 @@
     <t>52,185 patients represented in the Medicaid APCD dataset</t>
   </si>
   <si>
-    <t>Khan et al. [42]</t>
+    <t>Khan et al. [56]</t>
   </si>
   <si>
     <t>Administrative ICD-9 billing-code data derived from the Oregon Health &amp; Science University Hospital EHR system, validated through complete medical-chart review.</t>
@@ -282,7 +282,7 @@
     <t xml:space="preserve">2,399 adults with at least one congenital heart-disease ICD-9 code were identified; 2,193 formed the evaluated cohort after exclusions, of whom 1,069 had confirmed congenital heart disease. </t>
   </si>
   <si>
-    <t>Chughtai et al. [37]</t>
+    <t>Chughtai et al. [51]</t>
   </si>
   <si>
     <t>912,478 Medicaid enrollees with OUD in TAF , aged 12-64, non-dual, full-benefit; Transformed Medicaid Statistical Inform</t>
@@ -294,7 +294,7 @@
     <t>20,521,976 Medicaid enrollees in TAF, including 912,478 enrollees with opioid-use disorder; the MODRN comparison contained 21,185,130 enrollees, including 1,034,412 with opioid-use disorde</t>
   </si>
   <si>
-    <t>Laws et al. [43]</t>
+    <t>Laws et al. [57]</t>
   </si>
   <si>
     <t xml:space="preserve">2013 Rhode Island Medicaid claims submitted by three primary-care practice sites, compared with programmatically extracted EHR data from the same sites; selected discrepant records underwent manual EHR review. </t>
@@ -306,7 +306,7 @@
     <t>21,030 adult Rhode Island Medicaid beneficiaries receiving care from three primary-care practices.</t>
   </si>
   <si>
-    <t>Ditscheid et al. [45]</t>
+    <t>Ditscheid et al. [59]</t>
   </si>
   <si>
     <t xml:space="preserve">scientific data warehouse of BARMER,  one large German statutory health-insurance fund, covering outpatient physician services, prescription drugs, remedies, medical aids, hospital cases and inpatient procedures. </t>
@@ -321,7 +321,7 @@
     <t xml:space="preserve">This paper uses: Outpatinet physician care, outpatient treatment cases , and billing data so this was categorized under General category. </t>
   </si>
   <si>
-    <t>Hartmann et al. [46]</t>
+    <t>Hartmann et al. [60]</t>
   </si>
   <si>
     <t>2012 AOK Baden-Württemberg statutory health-insurance routine claims, primarily gender-specific outpatient diagnoses, with associated outpatient billing items, physician-specialty information and insured-person master data used for internal validation.</t>
@@ -333,7 +333,7 @@
     <t>3.8 million insured persons (AOK Baden-Württemberg, 2012 data)</t>
   </si>
   <si>
-    <t>Winkler et al. [47]</t>
+    <t>Winkler et al. [61]</t>
   </si>
   <si>
     <t>Individual-level routine claims supplied by 49 German statutory health-insurance funds for TIM-HF2 participants, linked with TIM-HF2 primary clinical-trial data.</t>
@@ -345,7 +345,7 @@
     <t xml:space="preserve">1,538 TIM-HF2 participants; approximately 95% were statutorily insured, and claims data were ultimately available for 1,450 participants. </t>
   </si>
   <si>
-    <t>Lloyd et al. [35]</t>
+    <t>Lloyd et al. [49]</t>
   </si>
   <si>
     <t xml:space="preserve">CMS national Medicaid MAX files, 2001–2013, and T-MSIS Analytic Files, 2014–2019, using inpatient, other-services and pharmacy claims or encounter files for Medicaid and Medicaid-expansion CHIP children. </t>
@@ -357,7 +357,7 @@
     <t>368,663,012 pediatric person-years (888 state-years); main comparison: 235,948,821 person-years</t>
   </si>
   <si>
-    <t>Wang et al. [38]</t>
+    <t>Wang et al. [52]</t>
   </si>
   <si>
     <t>Medicaid MAX Personal Summary and Other Therapy files for 2011–2012, and TAF Demographics and Enrollment and Other Services files for 2016–2018, covering fee-for-service claims and managed-care encounter records.</t>
